--- a/literature/literature-review.xlsx
+++ b/literature/literature-review.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Literature Review'!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Literature Review'!$A$1:$M$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -61,6 +61,10 @@
       <name val="Arial"/>
       <b val="1"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="12">
@@ -158,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -210,6 +214,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -575,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1349,8 +1359,320 @@
         </is>
       </c>
     </row>
+    <row r="13" ht="120" customHeight="1">
+      <c r="A13" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>boykoff2004</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>Boykoff, M. T. (Univ. of California, Santa Cruz, Environmental Studies), &amp; Boykoff, J. M. (American Univ., Dept. of Government)</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="n">
+        <v>2004</v>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>Balance as bias: global warming and the US prestige press</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>Global Environmental Change</t>
+        </is>
+      </c>
+      <c r="G13" s="23" t="inlineStr">
+        <is>
+          <t>14(2), 125–136</t>
+        </is>
+      </c>
+      <c r="H13" s="23" t="inlineStr">
+        <is>
+          <t>Climate communication / media framing of disasters</t>
+        </is>
+      </c>
+      <c r="I13" s="23" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.gloenvcha.2003.10.001</t>
+        </is>
+      </c>
+      <c r="J13" s="24" t="inlineStr">
+        <is>
+          <t>Content analysis of 636 articles (sampled from 3,543) in four U.S. prestige newspapers (New York Times, Washington Post, Los Angeles Times, Wall Street Journal), 1988–2002. Measure 1 (anthropogenic GW debate): 52.65% of articles gave roughly equal attention to anthropogenic causes and natural variation (journalistic 'balance'); 35.29% emphasized anthropogenic contributions; 6.18% emphasized natural variation/skepticism; 5.88% covered only anthropogenic causes. Chi-square tests show statistically significant divergence from the scientific consensus (IPCC) throughout 1990–2002. Measure 2 (action coverage): 78.20% balanced between cautious/voluntary and immediate/mandatory action; 11.17% cautious/voluntary only; 10.63% immediate/mandatory only. Significant divergence from scientific consensus on action 1989–2002. Conclusion: The journalistic norm of 'balance'—giving equal weight to a tiny minority of skeptics—creates an informational bias that misrepresents the scientific consensus and amplifies doubt about human-caused climate change.</t>
+        </is>
+      </c>
+      <c r="K13" s="24" t="inlineStr">
+        <is>
+          <t>Foundational study on how U.S. newspaper norms produce systematic bias in climate change coverage. Directly relevant as a methodological precedent: uses content analysis of the same prestige press examined in this project (NYT, WaPo, LAT, WSJ) and introduces the 'balance as bias' concept that explains why media coverage diverges from scientific consensus. Provides baseline (1988–2002) against which post-2000 disaster attribution coverage in this paper can be compared.</t>
+        </is>
+      </c>
+      <c r="L13" s="23" t="n">
+        <v>2947</v>
+      </c>
+      <c r="M13" s="24" t="inlineStr">
+        <is>
+          <t>Seminal piece on journalistic balance norm and climate misinformation; cite in introduction when establishing that media norms can distort disaster attribution coverage. Boykoff &amp; Boykoff (2007) is a follow-up showing balance norm largely disappeared by 2005—pair these two to frame the pre/post-2005 shift context for this study's 2000–2024 window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="120" customHeight="1">
+      <c r="A14" s="23" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>feldman2012</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>Feldman, L. (American Univ., School of Communication), Maibach, E. W. (George Mason Univ.), Roser-Renouf, C. (George Mason Univ.), &amp; Leiserowitz, A. (Yale Univ.)</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>Climate on Cable: The Nature and Impact of Global Warming Coverage on Fox News, CNN, and MSNBC</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>International Journal of Press/Politics</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="inlineStr">
+        <is>
+          <t>17(1), 3–31</t>
+        </is>
+      </c>
+      <c r="H14" s="23" t="inlineStr">
+        <is>
+          <t>Climate communication / media framing of disasters</t>
+        </is>
+      </c>
+      <c r="I14" s="23" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1177/1940161211425410</t>
+        </is>
+      </c>
+      <c r="J14" s="24" t="inlineStr">
+        <is>
+          <t>Content analysis of 269 cable news transcripts mentioning global warming (2007–2008): Fox News (n=182, 67.7%), CNN (n=66, 24.5%), MSNBC (n=21, 7.8%). Tone: Fox ~60% dismissive, &lt;20% accepting; CNN and MSNBC both &gt;70% accepting; 0% of MSNBC transcripts were dismissive. Scientific agreement: Fox most likely to challenge consensus; CNN most likely to affirm it. Climate reality: 33% of Fox broadcasts challenged reality of climate change; virtually none on CNN/MSNBC. Human causation: 14% of Fox affirmed human causation vs. 61% CNN, 33% MSNBC. Guest ratio: Fox 39.6% believers / 46.3% doubters; CNN 77.4% believers / 17.0% doubters. Survey (N=2,057): Fox viewing β = −0.10 (p&lt;.001) on global warming acceptance; CNN/MSNBC β = +0.08 (p&lt;.001)—effect size comparable to political partisanship. Cross-sectional data align with content patterns, suggesting media exposure shapes audience beliefs. Interactive effects show Republicans most influenced by outlet, consistent with biased processing among ideologically predisposed viewers.</t>
+        </is>
+      </c>
+      <c r="K14" s="24" t="inlineStr">
+        <is>
+          <t>Demonstrates that cable news outlet choice is associated with divergent climate beliefs, with effect sizes comparable to partisanship. Relevant to this project because it shows ideological differentiation in how media cover climate—a mechanism that could influence which outlets attribute disasters to climate change and how audiences receive that attribution. Methodologically comparable: content analysis + audience survey linking coverage characteristics to public perception.</t>
+        </is>
+      </c>
+      <c r="L14" s="23" t="n">
+        <v>707</v>
+      </c>
+      <c r="M14" s="24" t="inlineStr">
+        <is>
+          <t>Cite alongside Feldman et al. (2017) to demonstrate outlet-level ideological variation in climate coverage—cable news (2012) and prestige newspapers (2017) as complementary venues. Useful in the literature review section on media polarization of climate discourse. The survey component links outlet-level content differences to audience beliefs, supporting arguments about downstream effects of disaster attribution framing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="120" customHeight="1">
+      <c r="A15" s="23" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>feldman2017</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>Feldman, L. (Rutgers Univ., School of Communication and Information), Hart, P. S. (Univ. of Michigan, Ann Arbor), &amp; Milosevic, T. (Univ. of Oslo)</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>Polarizing news? Representations of threat and efficacy in leading US newspapers' coverage of climate change</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>Public Understanding of Science</t>
+        </is>
+      </c>
+      <c r="G15" s="23" t="inlineStr">
+        <is>
+          <t>26(4), 481–497</t>
+        </is>
+      </c>
+      <c r="H15" s="23" t="inlineStr">
+        <is>
+          <t>Climate communication / media framing of disasters</t>
+        </is>
+      </c>
+      <c r="I15" s="23" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1177/0963662515595348</t>
+        </is>
+      </c>
+      <c r="J15" s="24" t="inlineStr">
+        <is>
+          <t>Quantitative content analysis of 642 articles on climate change in four leading U.S. newspapers (NYT n=226, WP n=215, WSJ n=134, USA Today n=67), 2006–2011. Applies threat/efficacy framework (Extended Parallel Process Model). Key findings: WSJ was significantly less likely to discuss climate impacts (21.6%) compared to NYT, WP, and USA (~40–58%); WSJ was least likely to discuss present-day or U.S. impacts. Positive efficacy information was similarly rare across all papers (~20%). WSJ discussed negative response efficacy most frequently (32.1% vs. 15.8% WP). WSJ used conflict framing for actions significantly more than NYT (53% vs. 38%). WSJ used negative economic frames more than NYT and WP. Across all papers, impacts and actions were more likely discussed separately than together (only 31% of stories covered both). Conclusion: Systematic ideological differences in threat/efficacy representations appear in 'straight news' reporting, not only in opinion content, with WSJ consistently diverging in ways that may reduce reader concern and engagement.</t>
+        </is>
+      </c>
+      <c r="K15" s="24" t="inlineStr">
+        <is>
+          <t>Directly relevant as one of the few studies analyzing ideological variation in U.S. prestige newspaper coverage of climate change in the post-2005 era (2006–2011), overlapping with this project's 2000–2024 window. The threat/efficacy framework offers an analytical lens for understanding how disaster attribution is framed and whether papers convey urgency and agency. Demonstrates that WSJ coverage systematically diverges from other prestige papers—a finding directly applicable to cross-outlet comparisons in this study.</t>
+        </is>
+      </c>
+      <c r="L15" s="23" t="n">
+        <v>277</v>
+      </c>
+      <c r="M15" s="24" t="inlineStr">
+        <is>
+          <t>Cite in the literature review alongside Boykoff &amp; Boykoff (2004) to show evolution from balance-as-bias (pre-2005) to threat/efficacy framing differences (2006–2011) as the new dimension of ideological variation. Pair with Feldman et al. (2012) as the newspaper counterpart to the cable news study. Also cite when discussing how outlet-level framing choices shape public engagement and perception of disaster risk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="120" customHeight="1">
+      <c r="A16" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>boykoff2007</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>Boykoff, M. T. (Oxford Univ. Centre for the Environment, Environmental Change Institute)</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="n">
+        <v>2007</v>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>Flogging a dead norm? Newspaper coverage of anthropogenic climate change in the United States and United Kingdom from 2003 to 2006</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>39(4), 470–481</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>Climate communication / media framing of disasters</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1111/j.1475-4762.2007.00769.x</t>
+        </is>
+      </c>
+      <c r="J16" s="24" t="inlineStr">
+        <is>
+          <t>Content analysis of US (n=421) and UK (n=1,060) newspaper coverage of anthropogenic climate change, 2003–2006. US newspapers analyzed: Los Angeles Times (27%), New York Times (33%), USA Today (7%), Wall Street Journal (12%), Washington Post (21%). UK newspapers: Guardian/Observer (35%), Independent/Independent on Sunday (36%), The Times/Sunday Times (29%).
+US findings: US coverage diverged significantly from the scientific consensus in 2003 (36.6% balanced, z=7.73, p&lt;0.001) and 2004 (10.4% balanced, p&lt;0.05), but this divergence was no longer statistically significant in 2005 (8.2%) or 2006 (3.3%). Coverage of climate science depicting significant human contribution rose from 61.0% (2003) to 89.6% (2004) to 91.8% (2005) to 96.7% (2006).
+UK findings: No significant divergence from scientific consensus in any year (balanced coverage ≤1.7% throughout). UK coverage quadrupled over the study period; US coverage increased approximately 2.5×.
+Conclusion: The journalistic 'balance as bias' norm appears to have been effectively abandoned in US prestige press by 2005–2006 ('flogging a dead norm'), attributed to political, scientific, and ecological/meteorological events including the G8 Gleneagles summit, Hurricane Katrina, and An Inconvenient Truth. UK coverage was never significantly biased. Differs from Boykoff &amp; Boykoff (2004) which found significant divergence throughout 1988–2002.</t>
+        </is>
+      </c>
+      <c r="K16" s="24" t="inlineStr">
+        <is>
+          <t>The direct follow-up to Boykoff &amp; Boykoff (2004), documenting the erosion of the balance norm in US prestige press by 2005–2006. This is essential context for this paper's pre/post-2010 year trend: the balance era documented in boykoff2004 gave way to more consensus-aligned coverage by 2005–2006, setting the stage for the shift to net-positive attribution framing our data show beginning around 2010. The paper studies the same US newspapers (NYT, WaPo, LAT, WSJ) used throughout the prestige-press literature and directly informs the historical narrative of the year trend finding (Section 6).</t>
+        </is>
+      </c>
+      <c r="L16" s="24" t="n">
+        <v>773</v>
+      </c>
+      <c r="M16" s="24" t="inlineStr">
+        <is>
+          <t>Cite in the Discussion (Year Trend section) alongside boykoff2004 to complete the historical timeline: boykoff2004 establishes balance-norm bias through 2002; boykoff2007 shows the norm eroded by 2005–2006; our pre-2010 mean of −0.105 bridges these two findings before the post-2010 shift to net-positive. The pair of Boykoff papers can also be cited together as shorthand for 'the balance-norm era' when situating this paper's contribution relative to prior work in the introduction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="120" customHeight="1">
+      <c r="A17" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>mccright2011</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>McCright, A. M. (Michigan State Univ., Lyman Briggs College) &amp; Dunlap, R. E. (Oklahoma State Univ., Dept. of Sociology)</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="n">
+        <v>2011</v>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>The Politicization of Climate Change and Polarization in the American Public's Views of Global Warming, 2001–2010</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>The Sociological Quarterly</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="inlineStr">
+        <is>
+          <t>52(2), 155–194</t>
+        </is>
+      </c>
+      <c r="H17" s="24" t="inlineStr">
+        <is>
+          <t>Climate communication / media framing of disasters</t>
+        </is>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1111/j.1533-8525.2011.01198.x</t>
+        </is>
+      </c>
+      <c r="J17" s="24" t="inlineStr">
+        <is>
+          <t>Analyzes political polarization on climate change using data from 10 nationally representative Gallup Polls (2001–2010; pooled N up to 9,113). Four dependent variables: belief that global warming effects have already begun, belief that human activities are the primary cause, worry about global warming, and perceived threat to way of life.
+Key findings:
+1. Political divide: Liberals (68.82%) and Democrats (65.38%) are significantly more likely to believe global warming effects have already begun than conservatives (42.57%) and Republicans (41.84%), net of controls (education, understanding, age, gender, income, religiosity, race).
+2. Moderating effect of political orientation: The positive effects of educational attainment and self-reported understanding on climate beliefs and concern are present for liberals/Democrats, but weaker or negative for conservatives/Republicans. All 16 political orientation × knowledge interaction terms are statistically significant, consistent with the elite cues hypothesis and biased information processing.
+3. Growing polarization: The ideological gap on belief that warming has already begun grew from 18 percentage points in 2001 (67.1% liberals vs 49.4% conservatives) to 44 points in 2010 (74.8% vs 30.2%). The partisan gap grew from 11 points (60.4% Democrats vs 49.1% Republicans) to 41 points in 2010 (69.7% vs 29.0%). All 8 political orientation × year interaction terms are statistically significant (p&lt;.05 to p&lt;.001), confirming systematic ideological and partisan polarization over 2001–2010.</t>
+        </is>
+      </c>
+      <c r="K17" s="24" t="inlineStr">
+        <is>
+          <t>Provides the foundational empirical record of growing partisan polarization in U.S. public opinion on climate change over 2001–2010 — the same period in which our Attribution Index shifts from net-negative to net-positive. The paper's mechanism (a bifurcated flow of information from liberal vs. conservative elites and media) directly explains the supply-side logic behind our outlet-lean finding: if right-leaning outlets serve audiences whose climate beliefs are shaped by conservative elite cues, those outlets have demand-side incentives to produce less anthropogenic attribution framing. The 2001–2010 polarization trend also dovetails with the structural break in partisan climate discourse identified by Chinn et al. (2020) and the pre/post-2010 shift in our Attribution Index.</t>
+        </is>
+      </c>
+      <c r="L17" s="24" t="n">
+        <v>3366</v>
+      </c>
+      <c r="M17" s="24" t="inlineStr">
+        <is>
+          <t>Cite in the Related Literature (Climate Communication section) when motivating why outlet political lean predicts attribution framing — McCright &amp; Dunlap (2011) establish that the audience-level partisan divide in climate beliefs was growing throughout our sample period, consistent with a demand-side explanation for the lean gradient. Also cite in the Discussion (Outlet Lean section) alongside Gentzkow &amp; Shapiro (2010) and Carmichael et al. (2017) when distinguishing supply-side vs. demand-side explanations: if right-leaning outlet audiences hold weaker climate beliefs (McCright &amp; Dunlap 2011), outlets may supply less attribution framing to match audience expectations (Gentzkow &amp; Shapiro 2010).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:M1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/literature/literature-review.xlsx
+++ b/literature/literature-review.xlsx
@@ -162,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -218,6 +218,12 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1217,18 +1223,20 @@
           <t>Survey of text-as-data methods in economics. Provides standard three-step framework: (1) represent text as numerical array, (2) map array to predicted values of unknown outcome, (3) use predictions in further analysis. Notes most applications use ad hoc dictionary methods or penalized regression; published before the LLM-as-classifier wave (2019).</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>Standard methods citation for any text-as-data economics paper. Paper's pipeline maps onto this framework directly: (1) article text, (2) LLM-predicted attribution category/score, (3) aggregation into AttributionIndex_d and regressions. Paper's LLM-codebook approach is a methodological contribution relative to the pre-2019 landscape described here.</t>
+      <c r="K10" s="25" t="inlineStr">
+        <is>
+          <t>Standard methods citation for any text-as-data economics paper. Paper's pipeline maps onto this framework directly: (1) article text, (2) LLM-predicted attribution category/score, (3) aggregation into AttributionIndex_d and regressions. Paper's LLM-codebook approach is a methodological contribution relative to the pre-2019 landscape described here.
+Also directly motivates the manual audit design: their recommendation to cross-check fitted values against human codes is the explicit basis for our 100-article post-hoc audit.</t>
         </is>
       </c>
       <c r="L10" s="13" t="n">
         <v>2378</v>
       </c>
-      <c r="M10" s="18" t="inlineStr">
+      <c r="M10" s="26" t="inlineStr">
         <is>
           <t>SUGGESTED SECTIONS: Cite early in Methods section (obligatory text-as-data methods citation); Discussion/Conclusion (methodological contribution).
-METHODOLOGICAL CONTRIBUTION FLAG: Published in 2019, before the LLM-as-classifier wave. Worth noting in Discussion/Conclusion that this paper's use of an LLM with a detailed codebook (closer to a sophisticated classifier than either ad hoc dictionary methods or classic penalized-regression ML) represents a methodological contribution relative to the approaches Gentzkow et al. survey.</t>
+METHODOLOGICAL CONTRIBUTION FLAG: Published in 2019, before the LLM-as-classifier wave. Worth noting in Discussion/Conclusion that this paper's use of an LLM with a detailed codebook (closer to a sophisticated classifier than either ad hoc dictionary methods or classic penalized-regression ML) represents a methodological contribution relative to the approaches Gentzkow et al. survey.
+ADDED (June 2026): Also cited for manual audit recommendation — Gentzkow et al. explicitly recommend cross-checking fitted values against human-produced codes as a validation best practice. Our 100-article post-hoc audit follows this recommendation directly; credited in both the Introduction and the Text-as-Data subsection of Related Literature.</t>
         </is>
       </c>
     </row>
